--- a/ksoft/docs/fields_details/jalmeida/RE0508-14082024-152514.xlsx
+++ b/ksoft/docs/fields_details/jalmeida/RE0508-14082024-152514.xlsx
@@ -5170,13 +5170,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BD72A014-F359-4E0A-B5B4-0E6168C5934D}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C9C0C55A-D12F-443B-9105-71DDF29E89E7}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{767CA624-FA8F-4CA3-B4A0-ECAFFC1B61A8}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6699ED38-4F05-453C-8431-C0CC5474DB22}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7EE244B9-B3FB-4EAB-9964-2B98768D3FA2}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{40C5EACF-ABD8-4C86-A86D-18223CE60F50}"/>
 </file>
--- a/ksoft/docs/fields_details/jalmeida/RE0508-14082024-152514.xlsx
+++ b/ksoft/docs/fields_details/jalmeida/RE0508-14082024-152514.xlsx
@@ -5170,13 +5170,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C9C0C55A-D12F-443B-9105-71DDF29E89E7}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BD72A014-F359-4E0A-B5B4-0E6168C5934D}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6699ED38-4F05-453C-8431-C0CC5474DB22}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{767CA624-FA8F-4CA3-B4A0-ECAFFC1B61A8}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{40C5EACF-ABD8-4C86-A86D-18223CE60F50}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7EE244B9-B3FB-4EAB-9964-2B98768D3FA2}"/>
 </file>